--- a/AAII_Financials/Quarterly/LPL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LPL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>LPL</t>
   </si>
@@ -656,540 +656,553 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3623900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3635500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4988400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4952300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4128200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4118600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5302300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5193600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4868100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3908600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5703400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3554700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3597800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3383000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5476200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4943100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4261600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4983000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6604900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5417400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5224200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5093200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5544600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5188000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4086400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3968400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5458400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5181300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4711000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5349700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5836100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4942900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4713400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4767100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6270900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6136300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5833400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6355900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7142400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6051400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3130500</v>
+      </c>
+      <c r="E9" s="3">
         <v>3132600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4305600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4140600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3753000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3614200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4692600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4551600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4422800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3746500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5037200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3527000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3728800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3677100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5491300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4906000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4052100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4353300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5618200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4436100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4136300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4181700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4520700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4537100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3987700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3734700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5074000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4912900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4287100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4773900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4838500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4223000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4321400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4311800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>5499300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>5031500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4501200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4808600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>5726100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>5205800</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>493400</v>
+      </c>
+      <c r="E10" s="3">
         <v>502900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>682800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>811700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>375100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>504400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>609700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>642000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>445300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>162100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>666200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-131100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-294100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-15100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>209400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>629700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>986700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>981300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1087800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>911600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1023800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>650900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>98700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>233600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>384400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>268400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>423900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>575800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>997700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>719900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>392100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>455400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>771700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1104800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1332200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1547400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1416200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>845600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,130 +1245,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>213400</v>
+      </c>
+      <c r="E12" s="3">
         <v>218300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>261400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>245100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>249800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>238400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>254900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>295100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>249500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>252800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>262700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>257100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>258100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>270700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>294000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>255200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>241800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>248500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>250300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>238000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>221300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>204100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>200400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>210600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>221400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>224200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>209800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>193800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>373400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>303100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>262900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>265800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>247700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>239500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>291700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>251700</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>274200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>255800</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>276900</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>268600</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,252 +1493,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E14" s="3">
         <v>10200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>151200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>9800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-554700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>27600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-6000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>97300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>19100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>35700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>63700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>18200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1038000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>15300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>29300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>29600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>79100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>8200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1398600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>127100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>38800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>28200</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>1200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>21400</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>22700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-7500</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>32500</v>
+        <v>637500</v>
       </c>
       <c r="E15" s="3">
+        <v>653200</v>
+      </c>
+      <c r="F15" s="3">
         <v>246400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>706700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>864500</v>
       </c>
-      <c r="H15" s="3">
-        <v>37300</v>
-      </c>
       <c r="I15" s="3">
+        <v>813400</v>
+      </c>
+      <c r="J15" s="3">
         <v>329000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>946100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1001800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>951800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>465200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>775800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>767800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>780900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>47800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>49000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>50300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>51300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>50300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>52600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>50100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>46700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>40300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>38900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>42200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>46800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>48000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>53900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>48000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>49500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>40100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>37200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>34500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>33400</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>30800</v>
       </c>
       <c r="AL15" s="3">
         <v>30800</v>
       </c>
       <c r="AM15" s="3">
+        <v>30800</v>
+      </c>
+      <c r="AN15" s="3">
         <v>29900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>31300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>27900</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1787,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>3693500</v>
+      </c>
+      <c r="E17" s="3">
         <v>3539100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4871700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4645500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4213900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4095800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5246100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5254900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4936000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4257900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5601800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4046600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4267000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4225400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7171000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5505400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4637200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4954000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6262000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5026300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4704500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4711600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5072000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5091000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4563600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4280500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7215600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5697100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5040400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5475600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5640400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4830600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4933200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4849700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6228300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5621800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5147100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5454500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>6321000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5764300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-69600</v>
+      </c>
+      <c r="E18" s="3">
         <v>96400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>116700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>306800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-85700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>22700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-61400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-68000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-349300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>101600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-491800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-669300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-842400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1694800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-562300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-375600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>29100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>342900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>391100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>519700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>381600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>472600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>97000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-477200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1757200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-515800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-329400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-125900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>195800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>112300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-219800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-82600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>42700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>514500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>686300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>901500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>821400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>287100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,618 +2082,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E20" s="3">
         <v>337500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>117900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>164500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-385100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>278600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-90300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>96000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>142900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-73100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>98800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-162200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>180600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>397800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-162200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>56300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>65600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-96100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>155000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-25700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-57200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-81900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>18600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>125700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-35700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>32700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>25800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>16100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-47700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>21200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>13500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>32900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>64600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-106000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>159200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-38200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-208600</v>
+        <v>431000</v>
       </c>
       <c r="E21" s="3">
+        <v>412100</v>
+      </c>
+      <c r="F21" s="3">
         <v>245200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>849000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1163800</v>
       </c>
-      <c r="H21" s="3">
-        <v>68800</v>
-      </c>
       <c r="I21" s="3">
+        <v>844900</v>
+      </c>
+      <c r="J21" s="3">
         <v>106600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>975000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>837800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>459600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>639800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>185100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>260700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-242100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-483700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>115400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>554800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>997500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1122200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1421500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1295900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1136200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1196400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>909900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>257100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>647200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-935800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>383400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>433300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>638200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>930000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>817200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>496100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>703100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>835400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1281400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1436600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1439800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1628600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>879200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E22" s="3">
         <v>96800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>111200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>118600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>128800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>136500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>148700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>177800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>172800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>162500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>165600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>148100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>126000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>109900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>97900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>77700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>69900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>65900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>68700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>89700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>81200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>84900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>83100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>86200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>56500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>61200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>54200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>51100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>28900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>17000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>15100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>14800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>19100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>17500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>20500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>18900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>23200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>22600</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-296500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-343100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-257400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>732900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-380700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-157800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-314000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-736200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-747600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-666000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1131100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1394900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-802100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-389200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>28800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>178100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>456400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>412800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>239500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>307600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-41800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-515100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-247700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1847000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-534200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-389300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-117100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>196700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>89300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-285600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-80500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>38700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>526900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>732000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>772300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>958100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>223600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E24" s="3">
         <v>35100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>74700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>60100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>187400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>99700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-169700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-24300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-171600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-135400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-246800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>175400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-237100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-98800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-13000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>42800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>108600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>94700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-147800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-50400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-127100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-80600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-302500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-140600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>94800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-60100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>68500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>75100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-33200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-39300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>106900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>83700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>160800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>215800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>53000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2781,252 +2830,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-270500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-378200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-243300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>658200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-161000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-568000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-257400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-341700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-566500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>39000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-576000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-530500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-884400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1570400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-565000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-290300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>41800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>135300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>347800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>318100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>196900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>455400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-387900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-167100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1544500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-393600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-484200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>128200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>14200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-252500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-41100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>38400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>420000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>648300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>611500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>742200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>170600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-261300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-374900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-246700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>639700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-178400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-621300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-270400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-367600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-582700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>44900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-534900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-651500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-930900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1423100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-576300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-307500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>131700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>314900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>272500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>169000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>416500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>23400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-376600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-167200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1530900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-373200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-482600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-55400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>122800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-249800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-49900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>32500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>388900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>607500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>570100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>718200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>160000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3147,8 +3205,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3269,8 +3330,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3391,8 +3455,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3513,252 +3580,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-136900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-337500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-117900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-164500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>385100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-278600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>90300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-96000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-142900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>73100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-98800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>162200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-180600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-397800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>162200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-56300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-65600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>96100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-155000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>25700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>57200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>81900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>52600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-18600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-125700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>35700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-32700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>31000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-16100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>8200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>47700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-21200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-13500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-32900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-64600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>106000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-159200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-261300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-374900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-246700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>639700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-178400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-621300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-270400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-367600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-582700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>44900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-534900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-651500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-930900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1423100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-576300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-307500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>131700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>314900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>272500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>169000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>416500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>23400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-376600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-167200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1530900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-373200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-482600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-55400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>122800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-249800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-49900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>32500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>388900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>607500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>570100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>718200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>160000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3879,257 +3955,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-261300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-374900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-246700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>639700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-178400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-621300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-270400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-367600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-582700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>44900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-534900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-651500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-930900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1423100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-576300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-307500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>131700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>314900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>272500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>169000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>416500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>23400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-376600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-167200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1530900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-373200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-482600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-55400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>122800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-249800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-49900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>32500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>388900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>607500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>570100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>718200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>160000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4172,8 +4257,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4216,1106 +4302,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>937100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1000900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1089000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1102500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1230600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>666400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1368500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1360300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1432600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1913600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1740900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2233200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1805800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1697000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1368500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1124800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2082900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2591100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2656200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2608200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2710700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2889000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3121400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2532600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2711000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2989000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2835600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2456100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2132600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2187800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1986600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2235800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2395200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2206400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2290300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1737200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1210300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1402800</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>968300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E42" s="3">
         <v>4500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>50000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>57500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>42500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>101400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>133800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>52600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>112400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>599400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>805200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>387300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>144900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1295200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>200400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>216300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>217300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>1100</v>
       </c>
       <c r="AA42" s="3">
         <v>1100</v>
       </c>
       <c r="AB42" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC42" s="3">
         <v>1200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>228500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>669700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>603000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1105000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>870900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>797300</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>982200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1285600</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1569100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1565700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1798400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2454800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1791200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2467000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2653400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2446000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2938100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2407900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2603100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1962400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2880700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2015800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1924000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2315700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2269300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3007000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3544500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3297600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3237500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3298900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2735400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3052100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2294900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2506300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3107100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3642900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2552200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3213100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2532300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2751000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3073400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3055600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3965900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4359300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>4020800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>4095800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>4598400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3817600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1996800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1830800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1763500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2197000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2119600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2007300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1808300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2541600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2236400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2507100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1949300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2487500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2036000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2155600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2154700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3297600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3589100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3256800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2512800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2685200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2042100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1740200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1606300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1847800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1570300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1940500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1743500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2427200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2260900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2393200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2260600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2095800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2041500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1974300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2068100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2344300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2062200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2054900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2059000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2242800</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E45" s="3">
         <v>284200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>135800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>197500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>186500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1701300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>888700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1005000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>324700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>52900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>230000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>621800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1131700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>154700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1435500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1644000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>953900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1259600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1173600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1192200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1103100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1071100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>749200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>975400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>988800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1096300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1023600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1066900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>963600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>859300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>608900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>402500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>423500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>408800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>289600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>428200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>485800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>524200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>393400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>522400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4766800</v>
+      </c>
+      <c r="E46" s="3">
         <v>4686200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4836800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6009400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5370400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6943300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6852600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7504300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7120200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7582200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7328400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7804600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8089500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7557100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7083000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8598400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9112500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10116100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9890300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9784900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9095300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9000700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8213600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8408900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7566200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8533300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8711100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9593900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7910500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8657400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7392100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7488700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8162200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8314800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9216900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>9974000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>8794500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>8682400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>9435800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>8836700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>196700</v>
+      </c>
+      <c r="E47" s="3">
         <v>105800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>159400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>120900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>112400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>150300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>152100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>127700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>161400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>163000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>160000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>191500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>195500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>142900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>285400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>460500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>315400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>243800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>248700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>265800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>239500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>259600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>285300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>193100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>221000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>293000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>285600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>232300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>188600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>190100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>164300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>158600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>154000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>137700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>149900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>137500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>127800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>149500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>197500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>224000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>9106300</v>
+      </c>
+      <c r="E48" s="3">
         <v>9387000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10024600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10629900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11355400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11119200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11645200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13300000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13790400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14640600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15577500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15565100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15820300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16239200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15731400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16628600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16293400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15937400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15418800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15238500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>15174900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14950700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>15231100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16270000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16728400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18739300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18774500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>21120200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>21068600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>21027600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18144100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>16307900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>15987500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14721100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>14257700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>13203600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12466000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>11656300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>10828300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>10247700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1245700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1213600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>599800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1090000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1159600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1031000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>664200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1257600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>754400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>809700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>873300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>817500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>828900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1327800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1314700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1351000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1318300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1251200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1233700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1158400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>928400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>931700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>763800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>611500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>652500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>738900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>742400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>864600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>819600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>897600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>829600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>803500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>795000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>766200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>803300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>782000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>744500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>764600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>805400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>766400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5436,8 +5550,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5558,130 +5675,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E52" s="3">
         <v>255000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>168200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>95900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>98100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>112700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>156700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>235300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>311900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>343400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>368600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>336300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>359200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>456500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2349900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2259300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2072500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1917200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1824400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1757100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1804700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1791500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1791700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1849500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1823600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1839400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1724800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1513300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1341400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1430400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1337500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1258100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1314600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1256200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1232800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1239600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1188500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1071800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1128900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1138400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5802,130 +5925,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>17758200</v>
+      </c>
+      <c r="E54" s="3">
         <v>17931600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18646600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20439400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20676900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21721000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22243700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25239400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25452700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26870800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27575900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27884800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28374900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28104200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26764500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29297800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29112100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29465700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>28615900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>28204600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27242800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26934200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>25948800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>27333000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>26991800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30143900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30238400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33324300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>31328700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32203100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>27867600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26016900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>26413100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>25196000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>25660500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>25336700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>23321100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>22324700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>22395900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>21213300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5968,8 +6097,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6012,740 +6142,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>2035300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1798500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2291100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3011300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2629700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2087000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2812500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3116100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3215700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3297400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3217700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3491900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3399400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3018300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3046300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3671100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3413400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4058100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3610500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3247100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2802400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2941400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2796700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3108600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2669000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2412600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2225500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2379300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2477500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2702900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2593500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2573100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2494500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2354400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2530100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2607300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2150400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2193700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2589600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2762800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>3951800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3202300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2631300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3876000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4103000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5446300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4418600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4817600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4341200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4397100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4052300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4050400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3794700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4042500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4106100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3801500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4604100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3738500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3035800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3716600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3328800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2746500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2320800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1982600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2413500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2427500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1680500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1708400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1625800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1454900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1305300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1659500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1833200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1804300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1278600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1072600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>734100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>690200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>601100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1001400</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1114200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1019900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1183400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1239500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1546300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2899000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3074900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3125100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2406900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2181200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2937000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2740900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2344600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2252400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3318800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3450300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3363900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3395600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3849800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3286100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3342400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3190600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3027700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3534600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3511000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4579200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5431200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5382700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4890500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4697300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4463000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3983800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3878000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3862100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4092600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3429700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3088300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3298400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3161700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2603600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>7509500</v>
+      </c>
+      <c r="E60" s="3">
         <v>6382300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6648000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8612600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8686300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10796000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10735500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11541400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10421300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10317000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10707500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10815700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10023600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9784800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10471100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10922900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11381500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11192300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10496100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10249800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9473600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8878600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8145100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8625800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8593500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9419300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9337200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9470400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8993900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8855100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8361800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8216400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8205600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8020800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7901200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7109600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5972800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6182300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>6352400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>6367800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>4736800</v>
+      </c>
+      <c r="E61" s="3">
         <v>5861200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6189700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5781600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5934200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5193000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5477300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6567500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7440100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8343300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8799700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9004400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9515700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9205900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7192000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7429200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6094200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6384800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6525300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6443800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7098900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7907800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8151900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9159100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8930300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9876300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9853500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10332500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8500600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8383100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5884100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4588400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4522600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3850300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3652200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3665600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3685800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3525400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3699800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3312300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>571500</v>
+      </c>
+      <c r="E62" s="3">
         <v>580900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>377500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>410000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>441400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>411500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>565400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>776300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>927900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1109400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1302500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1457500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1610700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1033400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>611900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>518600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>517400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>525600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>522600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>552300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>349800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>350900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>230500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>173800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>150400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>295300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>432600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>771400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>873000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1051400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1117300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1311500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1477300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>871400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>923400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1213500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>823900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>278900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>227600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>461700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6866,8 +7015,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6988,8 +7140,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7110,130 +7265,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>12818600</v>
+      </c>
+      <c r="E66" s="3">
         <v>12825200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13215900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14805000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15062700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16401300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16779000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18886900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18791100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19772000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20812500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21280800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21153700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20029200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19354800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20168200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19285500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19419800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18776700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18456500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18046500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18185900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17516200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18916300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18633900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>20594100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20599000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21627400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19428300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19398500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16125100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14841500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14696300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13236700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13011900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12546500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>10999900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>10453700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>10735500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>10555600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7276,8 +7437,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7398,8 +7560,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7520,8 +7685,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7642,8 +7810,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7764,130 +7935,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-432700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-192300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>195300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>428400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>432400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-190900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>745000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1002900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1406300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2063600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1907100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2495900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3179500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4019800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5313200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6135400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6410400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6406100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6395000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6082000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5734100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5563900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5268300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5245500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6134100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6377800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8189400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8467600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9261100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8601600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8163200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8465600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8718500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9347000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9312600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8926100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8509500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>8103900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>7277000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -8008,8 +8185,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8130,8 +8310,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8252,130 +8435,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>4068800</v>
+      </c>
+      <c r="E76" s="3">
         <v>4243400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4575000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4792800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4790400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4260500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4428700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5313300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5539100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5906700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5577100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5427700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5997500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6877500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7409700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9129600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9826600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10045900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9839100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9748100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9196300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8748300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8432700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8416700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8357900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9549800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9639400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11696900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11900400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12804600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11742500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11175400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11716800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11959300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12648700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12790200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12321300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11871000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11660400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>10657700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8496,257 +8685,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-261300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-374900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-246700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>639700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-178400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-621300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-270400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-367600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-582700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>44900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-534900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-651500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-930900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1423100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-576300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-307500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>131700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>314900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>272500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>169000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>416500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>23400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-376600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-167200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1530900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-373200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-482600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-55400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>122800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-249800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-49900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>32500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>388900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>607500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>570100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>718200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>160000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8789,130 +8987,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>730300</v>
+      </c>
+      <c r="E83" s="3">
         <v>813400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>375300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>766200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>854400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>815700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>517900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>410100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>767800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>780900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>408400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>801200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>887600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>965200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>813300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>839900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>874000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>902800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>875500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>875400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>801900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>811800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>805800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>865500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>715700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>833700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>857000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>866500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>793700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>738200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>718200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>713100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>763600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>764500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>779200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>734000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>685600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>644300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>648000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9033,8 +9235,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9155,8 +9360,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9277,8 +9485,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9399,8 +9610,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9521,130 +9735,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>722700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-80500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1031600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>441700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-267600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>410500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>920400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>548900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>540100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-307500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>391000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>734300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>577600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-439900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>814800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>599400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>310200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>535400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1519000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>989000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1085500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>712000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>813400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>338800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>433500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>155100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1243600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-41400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1290100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-160200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>648900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1193300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1206300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>673900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1444800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1696700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1718000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1117800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1214000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>962900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9687,130 +9907,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-295800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-291600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-212700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-270000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-216700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-250200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-192400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-455300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-258300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-663400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-553200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-433700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-667000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-999300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1503826000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1825540000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1291739000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1288757000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1022571000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1032246000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-648500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-422100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-322700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-260300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-617100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-863500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-852300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1433300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1942100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1917300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1586500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1690900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1806400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1525000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1578600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1299500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1506800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1551200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1138000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-939000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9931,8 +10155,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10053,130 +10280,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-414600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-355800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-259700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-344400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>221400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-284900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-225700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-184600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-60500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-523800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-430900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-183200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-657600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-703900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1107300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1880500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1102300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-921900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-739800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-724400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-874500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-847100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-188600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-285000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-680100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-681400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-894100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1314600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1838600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1944700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1684900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1584800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1476200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1642700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1142700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1630900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1668900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1289500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-690000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-862200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10219,8 +10452,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -10263,8 +10497,8 @@
       <c r="P96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10341,8 +10575,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10463,8 +10700,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10585,8 +10825,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10707,370 +10950,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-379200</v>
+      </c>
+      <c r="E100" s="3">
         <v>357400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-785900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-216500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-389000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-732000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-246900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-950500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1027700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-509100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-124200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>265100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1402900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>596100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>365800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>285300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>211500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-750800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-465300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-461100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-170100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>132900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-252200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>249300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>635000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>180000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1640500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>564500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2085200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>703200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>373100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>452700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>937500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>329400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>290500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>89200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>50900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-190200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>35400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-86700</v>
+      </c>
+      <c r="E101" s="3">
         <v>3500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>109200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-41500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>37200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>37400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-28300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>39500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-59300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>38500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-96200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>37700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>32600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>41800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-90700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>39500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>32100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>39100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>19700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>98300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>32700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>72800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-70300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>19900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>78000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-39600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>14900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>55400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-55600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>51600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-78400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>26200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>33000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-71800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>100700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-31800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-83100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-521900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>130300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>71800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>76000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-433700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>233800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-577400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>466300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>125800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>297600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>212900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-875800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-474600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-135900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>48000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-102500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-217300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-232400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>687400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-178400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-28900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>186800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>489900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>299300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>35600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-332000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-73900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>188800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>20300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>553100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>382400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>171400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>434500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>90100</v>
       </c>
     </row>
